--- a/Dokumentaion/Anforderungsanalyse.xlsx
+++ b/Dokumentaion/Anforderungsanalyse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/salome/Desktop/AL/Projektarbeit_Verwaltungssystem/Dokumentaion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF8F7C2-88EE-4048-811D-0AD86B67A49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C496D32-0820-1048-B67F-665DE543FCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="17500" activeTab="1" xr2:uid="{C0BB8202-58BD-4646-8C39-A324F048AB56}"/>
+    <workbookView xWindow="9540" yWindow="860" windowWidth="20480" windowHeight="17500" activeTab="1" xr2:uid="{C0BB8202-58BD-4646-8C39-A324F048AB56}"/>
   </bookViews>
   <sheets>
     <sheet name="Nicht funktional" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
   <si>
     <t>Analyse der Aktivitäten</t>
   </si>
@@ -480,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -528,9 +528,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -558,6 +555,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1287,11 +1289,11 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -1321,16 +1323,16 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>54</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E6" s="18">
@@ -1342,13 +1344,13 @@
       <c r="G6" s="19">
         <v>12</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="23" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
-      <c r="B7" s="25"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="8" t="s">
         <v>51</v>
       </c>
@@ -1364,11 +1366,11 @@
       <c r="G7" s="14">
         <v>8</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
-      <c r="B8" s="25"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="8" t="s">
         <v>52</v>
       </c>
@@ -1384,11 +1386,11 @@
       <c r="G8" s="14">
         <v>8</v>
       </c>
-      <c r="H8" s="25"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
-      <c r="B9" s="26"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="8" t="s">
         <v>53</v>
       </c>
@@ -1396,7 +1398,7 @@
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
-      <c r="H9" s="26"/>
+      <c r="H9" s="25"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
@@ -1409,10 +1411,10 @@
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="23" t="s">
         <v>60</v>
       </c>
       <c r="C11" s="8" t="s">
@@ -1430,13 +1432,13 @@
       <c r="G11" s="14">
         <v>6</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="23" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
-      <c r="B12" s="25"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
@@ -1452,11 +1454,11 @@
       <c r="G12" s="10">
         <v>12</v>
       </c>
-      <c r="H12" s="25"/>
+      <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
-      <c r="B13" s="25"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="8" t="s">
         <v>62</v>
       </c>
@@ -1472,11 +1474,11 @@
       <c r="G13" s="10">
         <v>12</v>
       </c>
-      <c r="H13" s="26"/>
+      <c r="H13" s="25"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="9"/>
-      <c r="B14" s="26"/>
+      <c r="B14" s="25"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="14"/>
@@ -1485,10 +1487,10 @@
       <c r="H14" s="12"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="23" t="s">
         <v>61</v>
       </c>
       <c r="C15" s="8" t="s">
@@ -1506,13 +1508,13 @@
       <c r="G15" s="10">
         <v>12</v>
       </c>
-      <c r="H15" s="24" t="s">
+      <c r="H15" s="23" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="7"/>
-      <c r="B16" s="25"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="8" t="s">
         <v>24</v>
       </c>
@@ -1528,11 +1530,11 @@
       <c r="G16" s="14">
         <v>8</v>
       </c>
-      <c r="H16" s="25"/>
+      <c r="H16" s="24"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
-      <c r="B17" s="25"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="8" t="s">
         <v>25</v>
       </c>
@@ -1548,11 +1550,11 @@
       <c r="G17" s="14">
         <v>4</v>
       </c>
-      <c r="H17" s="25"/>
+      <c r="H17" s="24"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
-      <c r="B18" s="25"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="8" t="s">
         <v>26</v>
       </c>
@@ -1568,11 +1570,11 @@
       <c r="G18" s="10">
         <v>12</v>
       </c>
-      <c r="H18" s="25"/>
+      <c r="H18" s="24"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
-      <c r="B19" s="26"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="8" t="s">
         <v>27</v>
       </c>
@@ -1580,7 +1582,7 @@
       <c r="E19" s="14"/>
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
-      <c r="H19" s="26"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
@@ -1593,16 +1595,16 @@
       <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E21" s="14">
@@ -1614,13 +1616,13 @@
       <c r="G21" s="14">
         <v>3</v>
       </c>
-      <c r="H21" s="24" t="s">
+      <c r="H21" s="23" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
-      <c r="B22" s="28"/>
+      <c r="B22" s="27"/>
       <c r="C22" s="8" t="s">
         <v>34</v>
       </c>
@@ -1636,15 +1638,15 @@
       <c r="G22" s="10">
         <v>12</v>
       </c>
-      <c r="H22" s="25"/>
+      <c r="H22" s="24"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
-      <c r="B23" s="29"/>
+      <c r="B23" s="28"/>
       <c r="C23" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E23" s="14">
@@ -1656,7 +1658,7 @@
       <c r="G23" s="14">
         <v>8</v>
       </c>
-      <c r="H23" s="26"/>
+      <c r="H23" s="25"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
@@ -1669,10 +1671,10 @@
       <c r="H24" s="13"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="29" t="s">
         <v>42</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -1690,13 +1692,13 @@
       <c r="G25" s="10">
         <v>12</v>
       </c>
-      <c r="H25" s="24" t="s">
+      <c r="H25" s="23" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="7"/>
-      <c r="B26" s="31"/>
+      <c r="B26" s="30"/>
       <c r="C26" s="8" t="s">
         <v>41</v>
       </c>
@@ -1712,13 +1714,13 @@
       <c r="G26" s="14">
         <v>9</v>
       </c>
-      <c r="H26" s="25"/>
+      <c r="H26" s="24"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="7"/>
-      <c r="B27" s="32"/>
+      <c r="B27" s="31"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="14">
@@ -1730,7 +1732,7 @@
       <c r="G27" s="14">
         <v>9</v>
       </c>
-      <c r="H27" s="26"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="7"/>
@@ -1743,16 +1745,16 @@
       <c r="H28" s="13"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="30" t="s">
+      <c r="B29" s="29" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="5" t="s">
         <v>69</v>
       </c>
       <c r="E29" s="14">
@@ -1764,13 +1766,13 @@
       <c r="G29" s="10">
         <v>12</v>
       </c>
-      <c r="H29" s="24" t="s">
+      <c r="H29" s="23" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
-      <c r="B30" s="31"/>
+      <c r="B30" s="30"/>
       <c r="C30" s="8" t="s">
         <v>47</v>
       </c>
@@ -1786,19 +1788,21 @@
       <c r="G30" s="14">
         <v>9</v>
       </c>
-      <c r="H30" s="25"/>
+      <c r="H30" s="24"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
-      <c r="B31" s="32"/>
+      <c r="B31" s="31"/>
       <c r="C31" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="8"/>
+      <c r="D31" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="E31" s="14"/>
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
-      <c r="H31" s="26"/>
+      <c r="H31" s="25"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
@@ -1944,6 +1948,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="H6:H9"/>
     <mergeCell ref="B15:B19"/>
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="B25:B27"/>
@@ -1952,13 +1963,6 @@
     <mergeCell ref="H25:H27"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="H15:H19"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="H6:H9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup scale="59" orientation="landscape" r:id="rId1"/>
@@ -1967,6 +1971,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010047E1B4110D667F4BADC525742D5EE2E5" ma:contentTypeVersion="11" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="d4242f0faca51ba845790f185672872f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b989ebd0-cfbd-4347-a61d-09d2ec87900e" xmlns:ns3="26aae414-ca61-41d7-9f0a-f5a0a53751b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d27d03a123c6c0eefdfdcad7d866e60f" ns2:_="" ns3:_="">
     <xsd:import namespace="b989ebd0-cfbd-4347-a61d-09d2ec87900e"/>
@@ -2161,15 +2174,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2182,6 +2186,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCE1D4D9-536E-44FC-AB8C-AFFB6EA70127}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{081D83C2-850D-4599-9382-82FEB8EFCCA0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2200,14 +2212,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCE1D4D9-536E-44FC-AB8C-AFFB6EA70127}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD38C2A4-C3E7-42FB-A641-6C290BE0F460}">
   <ds:schemaRefs>

--- a/Dokumentaion/Anforderungsanalyse.xlsx
+++ b/Dokumentaion/Anforderungsanalyse.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/salome/Desktop/AL/Projektarbeit_Verwaltungssystem/Dokumentaion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C496D32-0820-1048-B67F-665DE543FCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1187C636-C2D3-514A-B0CE-670709CEF11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9540" yWindow="860" windowWidth="20480" windowHeight="17500" activeTab="1" xr2:uid="{C0BB8202-58BD-4646-8C39-A324F048AB56}"/>
+    <workbookView xWindow="6060" yWindow="500" windowWidth="22740" windowHeight="17500" activeTab="1" xr2:uid="{C0BB8202-58BD-4646-8C39-A324F048AB56}"/>
   </bookViews>
   <sheets>
     <sheet name="Nicht funktional" sheetId="2" r:id="rId1"/>
     <sheet name="Funktional" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Funktional!$A$1:$H$44</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="71">
   <si>
     <t>Analyse der Aktivitäten</t>
   </si>
@@ -132,9 +135,6 @@
   </si>
   <si>
     <t>Typ muss Text, Bild oder Dokument sein</t>
-  </si>
-  <si>
-    <t>Maximal 3 Tags pro Information</t>
   </si>
   <si>
     <t>Information wird dem Projekt zugeordnet</t>
@@ -265,8 +265,11 @@
     </r>
   </si>
   <si>
+    <t>Maximal 1-3 Tags pro Information</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Anforderung </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -274,7 +277,7 @@
         <color theme="9"/>
         <rFont val="Calibri (Textkörper)"/>
       </rPr>
-      <t>Umsetzung im ersten Schritt</t>
+      <t xml:space="preserve">Umsetzung im ersten Schritt | </t>
     </r>
     <r>
       <rPr>
@@ -294,25 +297,12 @@
       </rPr>
       <t>Umsetzung in zweitem Schritt</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>*PL und Mitarbeiter können Projektinformationen einsehen</t>
-  </si>
-  <si>
-    <t>*Übersicht enthält alle wichtigen Projektinformationen</t>
-  </si>
-  <si>
-    <t>*In der Augfabenstellung nicht explizit gefordert.</t>
+  </si>
+  <si>
+    <t>PL und Mitarbeiter können Projektinformationen einsehen</t>
+  </si>
+  <si>
+    <t>Übersicht enthält alle wichtigen Projektinformationen</t>
   </si>
 </sst>
 </file>
@@ -480,7 +470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -494,9 +484,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -528,6 +516,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -555,11 +546,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -582,15 +573,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>644622</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>76969</xdr:rowOff>
+      <xdr:colOff>3540222</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>26169</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>286789</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>113975</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2344189</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>63175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -613,8 +604,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7417955" y="5407121"/>
-          <a:ext cx="5868939" cy="2153670"/>
+          <a:off x="10576022" y="6782569"/>
+          <a:ext cx="5890567" cy="2272206"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -934,26 +925,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:7" s="1" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
@@ -968,11 +959,11 @@
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" ht="32" x14ac:dyDescent="0.2">
@@ -1239,7 +1230,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.1640625" customWidth="1"/>
@@ -1251,28 +1242,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
@@ -1289,11 +1280,11 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -1306,16 +1297,16 @@
       <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="13" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -1323,528 +1314,526 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="E6" s="16">
+        <v>3</v>
+      </c>
+      <c r="F6" s="16">
+        <v>4</v>
+      </c>
+      <c r="G6" s="17">
+        <v>12</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="31"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E7" s="12">
+        <v>2</v>
+      </c>
+      <c r="F7" s="12">
+        <v>4</v>
+      </c>
+      <c r="G7" s="12">
+        <v>8</v>
+      </c>
+      <c r="H7" s="23"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="31"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
+      <c r="F8" s="12">
+        <v>4</v>
+      </c>
+      <c r="G8" s="12">
+        <v>8</v>
+      </c>
+      <c r="H8" s="23"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="31"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="24"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="31"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="12">
+        <v>2</v>
+      </c>
+      <c r="F11" s="12">
         <v>3</v>
       </c>
-      <c r="F6" s="18">
-        <v>4</v>
-      </c>
-      <c r="G6" s="19">
-        <v>12</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="14">
-        <v>2</v>
-      </c>
-      <c r="F7" s="14">
-        <v>4</v>
-      </c>
-      <c r="G7" s="14">
-        <v>8</v>
-      </c>
-      <c r="H7" s="24"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="16">
-        <v>2</v>
-      </c>
-      <c r="F8" s="14">
-        <v>4</v>
-      </c>
-      <c r="G8" s="14">
-        <v>8</v>
-      </c>
-      <c r="H8" s="24"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="25"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="7"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="12"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="14">
-        <v>2</v>
-      </c>
-      <c r="F11" s="14">
-        <v>3</v>
-      </c>
-      <c r="G11" s="14">
+      <c r="G11" s="12">
         <v>6</v>
       </c>
-      <c r="H11" s="23" t="s">
-        <v>65</v>
+      <c r="H11" s="22" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="24"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="23"/>
       <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="14">
+      <c r="D12" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="12">
         <v>3</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="12">
         <v>4</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="8">
         <v>12</v>
       </c>
-      <c r="H12" s="24"/>
+      <c r="H12" s="23"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="17" t="s">
+      <c r="A13" s="31"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="14">
         <v>3</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="12">
         <v>4</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="8">
         <v>12</v>
       </c>
-      <c r="H13" s="25"/>
+      <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="9"/>
-      <c r="B14" s="25"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="12">
         <v>3</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="12">
         <v>4</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="8">
         <v>12</v>
       </c>
-      <c r="H15" s="23" t="s">
+      <c r="H15" s="22" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="7"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="8" t="s">
+      <c r="A16" s="31"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="7" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="12">
         <v>4</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="12">
         <v>2</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="12">
         <v>8</v>
       </c>
-      <c r="H16" s="24"/>
+      <c r="H16" s="23"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="8" t="s">
+      <c r="A17" s="31"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="12">
+        <v>4</v>
+      </c>
+      <c r="F17" s="12">
+        <v>1</v>
+      </c>
+      <c r="G17" s="12">
+        <v>4</v>
+      </c>
+      <c r="H17" s="23"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="31"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E18" s="12">
+        <v>3</v>
+      </c>
+      <c r="F18" s="12">
         <v>4</v>
       </c>
-      <c r="F17" s="14">
-        <v>1</v>
-      </c>
-      <c r="G17" s="14">
-        <v>4</v>
-      </c>
-      <c r="H17" s="24"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="14">
-        <v>3</v>
-      </c>
-      <c r="F18" s="14">
-        <v>4</v>
-      </c>
-      <c r="G18" s="10">
+      <c r="G18" s="8">
         <v>12</v>
       </c>
-      <c r="H18" s="24"/>
+      <c r="H18" s="23"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="8" t="s">
+      <c r="A19" s="31"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="25"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="24"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="7"/>
-      <c r="B20" s="11"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="9"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="12">
+        <v>1</v>
+      </c>
+      <c r="F21" s="12">
+        <v>3</v>
+      </c>
+      <c r="G21" s="12">
+        <v>3</v>
+      </c>
+      <c r="H21" s="22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="31"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D22" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="14">
-        <v>1</v>
-      </c>
-      <c r="F21" s="14">
+      <c r="E22" s="12">
         <v>3</v>
       </c>
-      <c r="G21" s="14">
+      <c r="F22" s="12">
+        <v>4</v>
+      </c>
+      <c r="G22" s="8">
+        <v>12</v>
+      </c>
+      <c r="H22" s="23"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="31"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="12">
+        <v>2</v>
+      </c>
+      <c r="F23" s="12">
+        <v>4</v>
+      </c>
+      <c r="G23" s="12">
+        <v>8</v>
+      </c>
+      <c r="H23" s="24"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="31"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="11"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="12">
         <v>3</v>
       </c>
-      <c r="H21" s="23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="7"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="14">
+      <c r="F25" s="12">
+        <v>4</v>
+      </c>
+      <c r="G25" s="8">
+        <v>12</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="31"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="12">
         <v>3</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F26" s="12">
+        <v>3</v>
+      </c>
+      <c r="G26" s="12">
+        <v>9</v>
+      </c>
+      <c r="H26" s="23"/>
+    </row>
+    <row r="27" spans="1:8" ht="11" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="31"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="12">
+        <v>3</v>
+      </c>
+      <c r="F27" s="12">
+        <v>3</v>
+      </c>
+      <c r="G27" s="12">
+        <v>9</v>
+      </c>
+      <c r="H27" s="24"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="31"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="11"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="12">
+        <v>3</v>
+      </c>
+      <c r="F29" s="12">
         <v>4</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G29" s="8">
         <v>12</v>
       </c>
-      <c r="H22" s="24"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="7"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="14">
-        <v>2</v>
-      </c>
-      <c r="F23" s="14">
-        <v>4</v>
-      </c>
-      <c r="G23" s="14">
-        <v>8</v>
-      </c>
-      <c r="H23" s="25"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="7"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="13"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="14">
-        <v>3</v>
-      </c>
-      <c r="F25" s="14">
-        <v>4</v>
-      </c>
-      <c r="G25" s="10">
-        <v>12</v>
-      </c>
-      <c r="H25" s="23" t="s">
+      <c r="H29" s="22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="32"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="7" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="14">
-        <v>3</v>
-      </c>
-      <c r="F26" s="14">
-        <v>3</v>
-      </c>
-      <c r="G26" s="14">
-        <v>9</v>
-      </c>
-      <c r="H26" s="24"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="14">
-        <v>3</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
-      </c>
-      <c r="G27" s="14">
-        <v>9</v>
-      </c>
-      <c r="H27" s="25"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="7"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="13"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E29" s="14">
-        <v>3</v>
-      </c>
-      <c r="F29" s="14">
-        <v>4</v>
-      </c>
-      <c r="G29" s="10">
-        <v>12</v>
-      </c>
-      <c r="H29" s="23" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="12">
         <v>3</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>3</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="12">
         <v>9</v>
       </c>
-      <c r="H30" s="24"/>
+      <c r="H30" s="23"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="8" t="s">
-        <v>48</v>
+      <c r="A31" s="32"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="25"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="24"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
+      <c r="A32" s="32"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="8"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="7"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="8"/>
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="8"/>
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="2"/>
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -1916,45 +1905,8 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="H6:H9"/>
     <mergeCell ref="B15:B19"/>
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="B25:B27"/>
@@ -1963,23 +1915,21 @@
     <mergeCell ref="H25:H27"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="H15:H19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="H6:H9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup scale="59" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="53" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010047E1B4110D667F4BADC525742D5EE2E5" ma:contentTypeVersion="11" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="d4242f0faca51ba845790f185672872f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b989ebd0-cfbd-4347-a61d-09d2ec87900e" xmlns:ns3="26aae414-ca61-41d7-9f0a-f5a0a53751b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d27d03a123c6c0eefdfdcad7d866e60f" ns2:_="" ns3:_="">
     <xsd:import namespace="b989ebd0-cfbd-4347-a61d-09d2ec87900e"/>
@@ -2174,6 +2124,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2186,14 +2145,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCE1D4D9-536E-44FC-AB8C-AFFB6EA70127}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{081D83C2-850D-4599-9382-82FEB8EFCCA0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2212,6 +2163,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCE1D4D9-536E-44FC-AB8C-AFFB6EA70127}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD38C2A4-C3E7-42FB-A641-6C290BE0F460}">
   <ds:schemaRefs>
